--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>315</v>
+        <v>284</v>
       </c>
       <c r="D2">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>228</v>
+        <v>342</v>
       </c>
       <c r="D3">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D2">
         <v>126</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D3">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H3">
         <v>426</v>
